--- a/customers/amir hosein.xlsx
+++ b/customers/amir hosein.xlsx
@@ -545,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -556,7 +556,7 @@
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -565,7 +565,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -581,8 +581,12 @@
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="7">
+        <f>C27</f>
+        <v>4891000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <f>B3+C3</f>
         <v>747000</v>
@@ -596,7 +600,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <f>A3+B4-C4</f>
         <v>712000</v>
@@ -610,7 +614,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <f t="shared" ref="A5:A15" si="0">A4+B5-C5</f>
         <v>852000</v>
@@ -626,7 +630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
         <v>902000</v>
@@ -642,7 +646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>957000</v>
@@ -658,7 +662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>3457000</v>
@@ -674,7 +678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>3501000</v>
@@ -690,7 +694,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>3691000</v>
@@ -706,7 +710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>4151000</v>
@@ -722,7 +726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>4186000</v>
@@ -738,7 +742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>4516000</v>
@@ -754,7 +758,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>4786000</v>
@@ -770,7 +774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>4891000</v>
@@ -784,7 +788,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <f>A15+B16-C16</f>
         <v>4891000</v>

--- a/customers/amir hosein.xlsx
+++ b/customers/amir hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t xml:space="preserve">قهوه  </t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
   </si>
 </sst>
 </file>
@@ -583,7 +586,7 @@
       </c>
       <c r="H2" s="7">
         <f>C27</f>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -791,17 +794,23 @@
     <row r="16" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <f>A15+B16-C16</f>
-        <v>4891000</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>4981000</v>
+      </c>
+      <c r="B16" s="6">
+        <v>90000</v>
+      </c>
       <c r="C16" s="6"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <f t="shared" ref="A17:A24" si="1">A16+B17-C17</f>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -811,7 +820,7 @@
     <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <f t="shared" si="1"/>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -821,7 +830,7 @@
     <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <f t="shared" si="1"/>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -831,7 +840,7 @@
     <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <f t="shared" si="1"/>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -841,7 +850,7 @@
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="1"/>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -851,7 +860,7 @@
     <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <f t="shared" si="1"/>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -861,7 +870,7 @@
     <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <f t="shared" si="1"/>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -871,7 +880,7 @@
     <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <f t="shared" si="1"/>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -881,7 +890,7 @@
     <row r="25" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="7">
         <f>SUM(B3:B24)</f>
-        <v>4926000</v>
+        <v>5016000</v>
       </c>
       <c r="C25" s="7">
         <f>SUM(C3:C24)</f>
@@ -895,7 +904,7 @@
       </c>
       <c r="C27" s="10">
         <f>A24</f>
-        <v>4891000</v>
+        <v>4981000</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
